--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272178</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272164</v>
+        <v>121272162</v>
       </c>
       <c r="B3" t="n">
-        <v>90458</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347164</v>
+        <v>347235</v>
       </c>
       <c r="R3" t="n">
-        <v>6560199</v>
+        <v>6560211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272162</v>
+        <v>121272164</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>90468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347235</v>
+        <v>347164</v>
       </c>
       <c r="R4" t="n">
-        <v>6560211</v>
+        <v>6560199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>121272170</v>
       </c>
       <c r="B5" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>90468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R2" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272164</v>
+        <v>121272178</v>
       </c>
       <c r="B4" t="n">
-        <v>90468</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347164</v>
+        <v>347163</v>
       </c>
       <c r="R4" t="n">
-        <v>6560199</v>
+        <v>6560198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272164</v>
+        <v>121272162</v>
       </c>
       <c r="B2" t="n">
-        <v>90468</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347164</v>
+        <v>347235</v>
       </c>
       <c r="R2" t="n">
-        <v>6560199</v>
+        <v>6560211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272162</v>
+        <v>121272170</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>105199</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347235</v>
+        <v>347170</v>
       </c>
       <c r="R3" t="n">
-        <v>6560211</v>
+        <v>6560193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>121272178</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272170</v>
+        <v>121272164</v>
       </c>
       <c r="B5" t="n">
-        <v>105186</v>
+        <v>90480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347170</v>
+        <v>347164</v>
       </c>
       <c r="R5" t="n">
-        <v>6560193</v>
+        <v>6560199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272162</v>
+        <v>121272164</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>90481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347235</v>
+        <v>347164</v>
       </c>
       <c r="R2" t="n">
-        <v>6560211</v>
+        <v>6560199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272170</v>
+        <v>121272178</v>
       </c>
       <c r="B3" t="n">
-        <v>105199</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347170</v>
+        <v>347163</v>
       </c>
       <c r="R3" t="n">
-        <v>6560193</v>
+        <v>6560198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272178</v>
+        <v>121272170</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>105200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347163</v>
+        <v>347170</v>
       </c>
       <c r="R4" t="n">
-        <v>6560198</v>
+        <v>6560193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272164</v>
+        <v>121272162</v>
       </c>
       <c r="B5" t="n">
-        <v>90480</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347164</v>
+        <v>347235</v>
       </c>
       <c r="R5" t="n">
-        <v>6560199</v>
+        <v>6560211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272164</v>
+        <v>121272162</v>
       </c>
       <c r="B2" t="n">
-        <v>90481</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347164</v>
+        <v>347235</v>
       </c>
       <c r="R2" t="n">
-        <v>6560199</v>
+        <v>6560211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>90484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R3" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +887,7 @@
         <v>121272170</v>
       </c>
       <c r="B4" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272162</v>
+        <v>121272178</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347235</v>
+        <v>347163</v>
       </c>
       <c r="R5" t="n">
-        <v>6560211</v>
+        <v>6560198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272162</v>
+        <v>121272170</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>105203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347235</v>
+        <v>347170</v>
       </c>
       <c r="R2" t="n">
-        <v>6560211</v>
+        <v>6560193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272170</v>
+        <v>121272162</v>
       </c>
       <c r="B4" t="n">
-        <v>105203</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347170</v>
+        <v>347235</v>
       </c>
       <c r="R4" t="n">
-        <v>6560193</v>
+        <v>6560211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272170</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272164</v>
+        <v>121272178</v>
       </c>
       <c r="B3" t="n">
-        <v>90484</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347164</v>
+        <v>347163</v>
       </c>
       <c r="R3" t="n">
-        <v>6560199</v>
+        <v>6560198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121272162</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
+        <v>90490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R5" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272170</v>
+        <v>121272162</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347170</v>
+        <v>347235</v>
       </c>
       <c r="R2" t="n">
-        <v>6560193</v>
+        <v>6560211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>90491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R3" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272162</v>
+        <v>121272170</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>105210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347235</v>
+        <v>347170</v>
       </c>
       <c r="R4" t="n">
-        <v>6560211</v>
+        <v>6560193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272164</v>
+        <v>121272178</v>
       </c>
       <c r="B5" t="n">
-        <v>90490</v>
+        <v>100371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347164</v>
+        <v>347163</v>
       </c>
       <c r="R5" t="n">
-        <v>6560199</v>
+        <v>6560198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272162</v>
+        <v>121272170</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347235</v>
+        <v>347170</v>
       </c>
       <c r="R2" t="n">
-        <v>6560211</v>
+        <v>6560193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272164</v>
+        <v>121272178</v>
       </c>
       <c r="B3" t="n">
-        <v>90491</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347164</v>
+        <v>347163</v>
       </c>
       <c r="R3" t="n">
-        <v>6560199</v>
+        <v>6560198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272170</v>
+        <v>121272164</v>
       </c>
       <c r="B4" t="n">
-        <v>105210</v>
+        <v>90491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347170</v>
+        <v>347164</v>
       </c>
       <c r="R4" t="n">
-        <v>6560193</v>
+        <v>6560199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272178</v>
+        <v>121272162</v>
       </c>
       <c r="B5" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347163</v>
+        <v>347235</v>
       </c>
       <c r="R5" t="n">
-        <v>6560198</v>
+        <v>6560211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272170</v>
+        <v>121272178</v>
       </c>
       <c r="B2" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347170</v>
+        <v>347163</v>
       </c>
       <c r="R2" t="n">
-        <v>6560193</v>
+        <v>6560198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>90491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R3" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272164</v>
+        <v>121272170</v>
       </c>
       <c r="B4" t="n">
-        <v>90491</v>
+        <v>105210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347164</v>
+        <v>347170</v>
       </c>
       <c r="R4" t="n">
-        <v>6560199</v>
+        <v>6560193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41110-2024 artfynd.xlsx
+++ b/artfynd/A 41110-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272178</v>
+        <v>121272164</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>90491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347163</v>
+        <v>347164</v>
       </c>
       <c r="R2" t="n">
-        <v>6560198</v>
+        <v>6560199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272164</v>
+        <v>121272162</v>
       </c>
       <c r="B3" t="n">
-        <v>90491</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347164</v>
+        <v>347235</v>
       </c>
       <c r="R3" t="n">
-        <v>6560199</v>
+        <v>6560211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272170</v>
+        <v>121272178</v>
       </c>
       <c r="B4" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347170</v>
+        <v>347163</v>
       </c>
       <c r="R4" t="n">
-        <v>6560193</v>
+        <v>6560198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121272162</v>
+        <v>121272170</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>105210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347235</v>
+        <v>347170</v>
       </c>
       <c r="R5" t="n">
-        <v>6560211</v>
+        <v>6560193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack Äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
